--- a/文档/传感器/语音控制模块/命令词播报词协议列表V3_中文模板.xlsx
+++ b/文档/传感器/语音控制模块/命令词播报词协议列表V3_中文模板.xlsx
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="75">
   <si>
     <t>语义标签</t>
   </si>
@@ -236,6 +236,13 @@
   </si>
   <si>
     <t>A5 FA 00 82 0B 00 2C FB</t>
+  </si>
+  <si>
+    <t>握手协议</t>
+  </si>
+  <si>
+    <t>A5 FA 00 80 0A 00 21 FB 芯片发送
+A5 FA 00 80 0A 00 22 FB 芯片接收</t>
   </si>
   <si>
     <t>中文命令词</t>
@@ -1084,7 +1091,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1132,6 +1139,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1452,8 +1462,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1647,12 +1657,20 @@
         <v>36</v>
       </c>
     </row>
+    <row r="11" ht="97.15" spans="1:7">
+      <c r="A11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C6 C7:C8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C8">
       <formula1>"唤醒词,命令词,负性词,播报语,欢迎语,休息语,增大音量,减小音量,最大音量,中等音量,最小音量,开播报,关播报"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E7:E8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E8">
       <formula1>"主,被"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1678,73 +1696,73 @@
     <row r="2" ht="17.6" spans="1:2">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1"/>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1"/>
       <c r="B5" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1"/>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1"/>
       <c r="B7" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1"/>
       <c r="B8" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1"/>
       <c r="B9" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1"/>
       <c r="B10" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1"/>
       <c r="B11" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1"/>
       <c r="B12" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" ht="14.65" spans="1:2">
       <c r="A13" s="1"/>
       <c r="B13" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" ht="14.6" spans="1:2">
@@ -1760,31 +1778,31 @@
     <row r="16" spans="1:2">
       <c r="A16" s="1"/>
       <c r="B16" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" ht="13.9" spans="1:2">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1"/>
       <c r="B18" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" ht="27.75" spans="1:2">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" ht="14.65" spans="1:2">
       <c r="A20" s="1"/>
       <c r="B20" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" ht="14.6" spans="1:2">
@@ -1794,25 +1812,25 @@
     <row r="22" ht="17.65" spans="1:2">
       <c r="A22" s="1"/>
       <c r="B22" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" ht="41.65" spans="1:2">
       <c r="A23" s="1"/>
       <c r="B23" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" ht="41.65" spans="1:2">
       <c r="A24" s="1"/>
       <c r="B24" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" ht="28.5" spans="1:2">
       <c r="A25" s="1"/>
       <c r="B25" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" ht="14.6" spans="1:2">
@@ -1820,37 +1838,37 @@
     </row>
     <row r="27" ht="17.6" spans="1:2">
       <c r="B27" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="B28" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="B29" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="B30" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" ht="69.4" spans="1:2">
       <c r="B31" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" ht="69.4" spans="1:2">
       <c r="B32" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" ht="84" spans="2:2">
       <c r="B33" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" ht="14.6"/>
@@ -1861,17 +1879,17 @@
     </row>
     <row r="36" spans="2:2">
       <c r="B36" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" ht="14.6" spans="2:2">
       <c r="B38" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" ht="14.6"/>
@@ -1882,7 +1900,7 @@
     </row>
     <row r="41" ht="14.6" spans="2:2">
       <c r="B41" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" ht="14.6"/>
@@ -1893,23 +1911,23 @@
     </row>
     <row r="44" ht="14.6" spans="2:2">
       <c r="B44" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" ht="14.6"/>
     <row r="46" ht="17.6" spans="2:2">
       <c r="B46" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" ht="28.5" spans="2:2">
       <c r="B47" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" ht="28.5" spans="2:2">
       <c r="B48" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
